--- a/docs/test-cases/SPM-85_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-85_Test_Cases.xlsx
@@ -29,7 +29,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -62,6 +62,9 @@
     <font>
       <name val="Arial"/>
       <color theme="1"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -147,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -217,6 +220,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -509,12 +515,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.75" customHeight="1" s="26">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>SPM-85: SPM-85: As a Safety Officer, I want to log in and see only what I need to review the operational safety of planned events so that I can do my job without access to functions that are not mine.</t>
         </is>
@@ -526,32 +532,32 @@
     </row>
     <row r="2" ht="12.75" customHeight="1" s="26"/>
     <row r="3" ht="12.75" customHeight="1" s="26">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>Sheet</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>Linked AC</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -578,27 +584,27 @@
           <t>TC01</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC01</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer can log in and is shown as a Safety Officer</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="30" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -617,27 +623,27 @@
           <t>TC02</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC02</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>The public Create an account form does not offer the Safety Officer role</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="30" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -656,27 +662,27 @@
           <t>TC03</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC03</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer's sidebar shows only Dashboard, Safety Checks, All Events and Notifications</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -695,27 +701,27 @@
           <t>TC04</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC04</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>The Safety Checks list shows the events waiting for a safety check, and not events still being planned</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="30" t="inlineStr">
         <is>
           <t>AC2, AC3</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Boundary</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -734,27 +740,27 @@
           <t>TC05</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC05</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer sees the attendance, sessions, accessibility requirements and booked venues with capacity and layout on the event's Overview</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -773,27 +779,27 @@
           <t>TC06</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC06</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer sees the event's equipment arrangements read-only</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="30" t="inlineStr">
         <is>
           <t>AC3, AC4</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -812,27 +818,27 @@
           <t>TC07</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC07</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer is offered no button that changes an event, its venue, its equipment or its registration</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>AC4, AC5</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -851,27 +857,27 @@
           <t>TC08</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC08</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer who types the address of the Edit event information page is refused and shown no form</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="30" t="inlineStr">
         <is>
           <t>AC4, AC7</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="30" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -890,27 +896,27 @@
           <t>TC09</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC09</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer who types the address of an assigning, reviewing or venue-approving screen sees an access-denied page</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>AC5, AC7</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -929,27 +935,27 @@
           <t>TC10</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC10</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer cannot reach the screens for reserving equipment or finding a venue, and sees why</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="30" t="inlineStr">
         <is>
           <t>AC4, AC5, AC7</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -968,27 +974,27 @@
           <t>TC11</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC11</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer never sees the names or needs of the people registered for an event</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>AC6, AC7</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1007,27 +1013,27 @@
           <t>TC12</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC12</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C15" s="30" t="inlineStr">
         <is>
           <t>The Safety Officer's Dashboard lists the events awaiting their safety check</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="30" t="inlineStr">
         <is>
           <t>AC2, AC3</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="30" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1046,27 +1052,27 @@
           <t>TC13</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC13</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>An Event Coordinator has no Safety Checks link and is refused the Safety Checks page</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F16" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
@@ -1085,55 +1091,59 @@
           <t>TC14</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC14</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t>The Operations Manager has no Safety Checks link and is refused the Safety Checks page</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>Acceptance Criteria</t>
         </is>
       </c>
       <c r="G17" s="30" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Updated</t>
         </is>
       </c>
       <c r="H17" s="30" t="n"/>
-      <c r="I17" s="30" t="n"/>
+      <c r="I17" s="30" t="inlineStr">
+        <is>
+          <t>Week 7 #5</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="12.75" customHeight="1" s="26"/>
     <row r="19" ht="12.75" customHeight="1" s="26"/>
     <row r="20" ht="12.75" customHeight="1" s="26">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
       <c r="C20" s="27" t="n"/>
       <c r="D20" s="28" t="n"/>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E20" s="29" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
@@ -1141,19 +1151,19 @@
       <c r="F20" s="28" t="n"/>
     </row>
     <row r="21" ht="30.75" customHeight="1" s="26">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>Safety Officer exists as a separate internal role that a user can log in with.</t>
         </is>
       </c>
       <c r="C21" s="27" t="n"/>
       <c r="D21" s="28" t="n"/>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E21" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC01
 SPM-85-TC02</t>
@@ -1162,19 +1172,19 @@
       <c r="F21" s="28" t="n"/>
     </row>
     <row r="22" ht="44.25" customHeight="1" s="26">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Given I am logged in as a Safety Officer, when I view the main navigation, then only the items defined for the Safety Officer role are shown.</t>
         </is>
       </c>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="28" t="n"/>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC03
 SPM-85-TC04
@@ -1184,19 +1194,19 @@
       <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="57.75" customHeight="1" s="26">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer can view the information needed for a safety review of an event: expected attendance, sessions and timings, accessibility requirements, venue bookings with capacity and layout, and equipment arrangements.</t>
         </is>
       </c>
       <c r="C23" s="27" t="n"/>
       <c r="D23" s="28" t="n"/>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC04
 SPM-85-TC05
@@ -1207,19 +1217,19 @@
       <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="57.75" customHeight="1" s="26">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer cannot edit event information, venue bookings, equipment arrangements or registrations.</t>
         </is>
       </c>
       <c r="C24" s="27" t="n"/>
       <c r="D24" s="28" t="n"/>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC06
 SPM-85-TC07
@@ -1230,19 +1240,19 @@
       <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="44.25" customHeight="1" s="26">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer cannot assign Coordinators, review event requests, approve venue bookings, reserve equipment or confirm events.</t>
         </is>
       </c>
       <c r="C25" s="27" t="n"/>
       <c r="D25" s="28" t="n"/>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E25" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC07
 SPM-85-TC09
@@ -1252,19 +1262,19 @@
       <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="17.25" customHeight="1" s="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer cannot view attendee personal details.</t>
         </is>
       </c>
       <c r="C26" s="27" t="n"/>
       <c r="D26" s="28" t="n"/>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC11</t>
         </is>
@@ -1272,19 +1282,19 @@
       <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="71.25" customHeight="1" s="26">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>AC7</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>Given a Safety Officer navigates directly to a screen outside their permissions, when the page loads, then they see an access-denied state and no restricted data is rendered.</t>
         </is>
       </c>
       <c r="C27" s="27" t="n"/>
       <c r="D27" s="28" t="n"/>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E27" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC08
 SPM-85-TC09
@@ -1295,19 +1305,19 @@
       <c r="F27" s="28" t="n"/>
     </row>
     <row r="28" ht="30.75" customHeight="1" s="26">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>AC8</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>Users in other roles cannot perform Safety Officer actions.</t>
         </is>
       </c>
       <c r="C28" s="27" t="n"/>
       <c r="D28" s="28" t="n"/>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC13
 SPM-85-TC14</t>
@@ -1317,12 +1327,12 @@
     </row>
     <row r="29" ht="12.75" customHeight="1" s="26"/>
     <row r="30" ht="219.75" customHeight="1" s="26">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>src/lib/roles.ts
 src/lib/permissions.ts
@@ -2388,7 +2398,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC09</t>
         </is>
@@ -2400,7 +2410,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer who types the address of an assigning, reviewing or venue-approving screen sees an access-denied page</t>
         </is>
@@ -2412,7 +2422,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -2424,7 +2434,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Type /assignments after the site address in the browser address bar (e.g. http://localhost:3000/assignments) and press Enter
 2. Type /queue after the site address in the browser address bar (e.g. http://localhost:3000/queue) and press Enter
@@ -2439,7 +2449,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Addresses: /assignments (assign Coordinators), /queue (review event requests), /bookings (approve venue bookings), /venues (venue catalogue)</t>
         </is>
@@ -2451,7 +2461,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 1: The Assignments page shows 'You do not have access to this' and a 'Back to Dashboard' button. No events or coordinators are listed.
 Step 2: The Review Queue page shows 'You do not have access to this'. No requests are listed.
@@ -2466,7 +2476,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -2498,7 +2508,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>/assignments, /queue, /bookings and /venues each showed 'You do not have access to this' with a 'Back to Dashboard' button, and no table rows.</t>
         </is>
@@ -2522,7 +2532,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2534,7 +2544,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -2565,7 +2575,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 1: The Assignments page shows 'You do not have access to this' and a 'Back to Dashboard' button. No events or coordinators are listed.
 Step 2: The Review Queue page shows 'You do not have access to this'. No requests are listed.
@@ -2592,7 +2602,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -2604,7 +2614,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -3631,7 +3641,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC10</t>
         </is>
@@ -3643,7 +3653,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer cannot reach the screens for reserving equipment or finding a venue, and sees why</t>
         </is>
@@ -3655,7 +3665,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -3667,7 +3677,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Type /equipment/requests after the site address in the browser address bar (e.g. http://localhost:3000/equipment/requests) and press Enter
 2. Click 'Safety Checks' in the sidebar
@@ -3682,7 +3692,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Addresses: /equipment/requests (reserve equipment), /events/&lt;reference&gt;/venue (find and request a venue)
 Event: SPM85 Harbour Safety Forum</t>
@@ -3695,7 +3705,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 1: The Equipment requests page shows 'Only Technical Support Staff can view equipment requests.' No events or equipment are listed, and there is no way to reserve anything.
 Step 4: The Find a venue page shows 'You do not have access to this' with 'Finding and booking a venue is for the Event Coordinator. The rooms booked for this event are on its Overview.' No venues are listed and there is no 'Request booking' button.</t>
@@ -3708,7 +3718,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -3740,7 +3750,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>/equipment/requests showed 'This queue is for Technical Support Staff.' and 'Only Technical Support Staff can view equipment requests.' with no rows. Typing /events/&lt;reference&gt;/venue showed 'You do not have access to this' with 'Finding and booking a venue is for the Event Coordinator. The rooms booked for this event are on its Overview.' - no venue named and no Request booking button.</t>
         </is>
@@ -3764,7 +3774,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>The Find a venue refusal is new in SPM-85: before it, the page loaded and then showed a load error.</t>
         </is>
@@ -3776,7 +3786,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -3807,7 +3817,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 1: The Equipment requests page shows 'Only Technical Support Staff can view equipment requests.' No events or equipment are listed, and there is no way to reserve anything.
 Step 4: The Find a venue page shows 'You do not have access to this' with 'Finding and booking a venue is for the Event Coordinator. The rooms booked for this event are on its Overview.' No venues are listed and there is no 'Request booking' button.</t>
@@ -3832,7 +3842,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>The Find a venue refusal is new in SPM-85: before it, the page loaded and then showed a load error.</t>
         </is>
@@ -3844,7 +3854,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -4871,7 +4881,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC11</t>
         </is>
@@ -4883,7 +4893,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer never sees the names or needs of the people registered for an event</t>
         </is>
@@ -4895,7 +4905,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. 'SPM85 Riverside Product Launch' has two registrations: Lee Wei Ming (dietary 'Vegetarian', accessibility 'Wheelchair user - front row please') and Anita Devi. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -4907,7 +4917,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM85 Riverside Product Launch'
@@ -4922,7 +4932,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Event: SPM85 Riverside Product Launch
 Registered attendees: Lee Wei Ming, Anita Devi</t>
@@ -4935,7 +4945,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 2: The Overview has no 'Attendees' tab, and 'Lee Wei Ming', 'Anita Devi', 'Vegetarian' and 'Wheelchair user - front row please' appear nowhere on the page.
 Step 3: None of those names or needs appear on the Equipment requirements page either.
@@ -4949,7 +4959,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -4981,7 +4991,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>On the Riverside launch's Overview (tabs Overview and Equipment) and Equipment page, none of 'Lee Wei Ming', 'Anita Devi', 'Vegetarian' or 'Wheelchair user - front row please' appeared. /registrations showed 'You do not have access to this' and no registrations.</t>
         </is>
@@ -5005,7 +5015,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5017,7 +5027,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -5048,7 +5058,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 2: The Overview has no 'Attendees' tab, and 'Lee Wei Ming', 'Anita Devi', 'Vegetarian' and 'Wheelchair user - front row please' appear nowhere on the page.
 Step 3: None of those names or needs appear on the Equipment requirements page either.
@@ -5074,7 +5084,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -5086,7 +5096,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -6113,7 +6123,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC12</t>
         </is>
@@ -6125,7 +6135,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>The Safety Officer's Dashboard lists the events awaiting their safety check</t>
         </is>
@@ -6137,7 +6147,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -6149,7 +6159,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Click 'Dashboard' in the sidebar</t>
         </is>
@@ -6161,7 +6171,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>In Safety review: SPM85 Harbour Safety Forum
 In Planning: SPM85 Marina Networking Night</t>
@@ -6174,7 +6184,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 1: The Dashboard has a list headed 'Awaiting your safety check' that includes 'SPM85 Harbour Safety Forum' with the status 'Safety review'. 'SPM85 Marina Networking Night' is not in that list.</t>
         </is>
@@ -6186,7 +6196,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -6218,7 +6228,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>The Dashboard's 'Awaiting your safety check' list included 'SPM85 Harbour Safety Forum' (Safety review, 27 Sept 2027, 09:00-17:00). 'SPM85 Marina Networking Night' was not in it.</t>
         </is>
@@ -6242,7 +6252,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6254,7 +6264,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -6285,7 +6295,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 1: The Dashboard has a list headed 'Awaiting your safety check' that includes 'SPM85 Harbour Safety Forum' with the status 'Safety review'. 'SPM85 Marina Networking Night' is not in that list.</t>
         </is>
@@ -6309,7 +6319,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -6321,7 +6331,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -7348,7 +7358,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC13</t>
         </is>
@@ -7360,7 +7370,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>An Event Coordinator has no Safety Checks link and is refused the Safety Checks page</t>
         </is>
@@ -7372,7 +7382,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. Logged in as Daniel Tan (Event Coordinator), who submitted 'SPM85 Harbour Safety Forum' for its safety check.</t>
         </is>
@@ -7384,7 +7394,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Look at the sidebar
 2. Type /safety-checks after the site address in the browser address bar (e.g. http://localhost:3000/safety-checks) and press Enter</t>
@@ -7397,7 +7407,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Coordinator: daniel.tan@connectsphere.com / password123
 Address: /safety-checks</t>
@@ -7410,7 +7420,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 1: The sidebar has no 'Safety Checks' link.
 Step 2: The Safety Checks page shows 'You do not have access to this' with 'The Operational Safety Check is the Safety Officer's role. You can still see the events you are involved in from your Dashboard.' 'SPM85 Harbour Safety Forum' is not listed.</t>
@@ -7423,7 +7433,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -7455,7 +7465,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Daniel Tan's sidebar: Dashboard, Review Queue, All Events, Venues, Equipment, Notifications - no Safety Checks. /safety-checks showed 'You do not have access to this' with 'The Operational Safety Check is the Safety Officer's role. You can still see the events you are involved in from your Dashboard.' The forum was not listed.</t>
         </is>
@@ -7479,7 +7489,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7491,7 +7501,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -7522,7 +7532,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 1: The sidebar has no 'Safety Checks' link.
 Step 2: The Safety Checks page shows 'You do not have access to this' with 'The Operational Safety Check is the Safety Officer's role. You can still see the events you are involved in from your Dashboard.' 'SPM85 Harbour Safety Forum' is not listed.</t>
@@ -7547,7 +7557,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -7559,7 +7569,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -8564,7 +8574,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="24.75" customWidth="1" style="26" min="1" max="1"/>
@@ -8572,248 +8582,254 @@
     <col width="12.63" customWidth="1" style="26" min="3" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="26">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1" ht="90" customHeight="1" s="26">
+      <c r="A1" s="31" t="inlineStr">
+        <is>
+          <t>v2 (2026-10-20): The Event Operations Manager is now shown as the 'Event Coordinator Lead' (SPM-84 AC1, forum #129, Week 7 Change #5) - the same role, accounts, permissions and pages. Read 'Operations Manager', 'Event Operations Manager' or 'Ops Manager' in this case as 'Event Coordinator Lead'; on screen the role is shown under its new name, and refusals say 'Assigning coordinators is the Event Coordinator Lead's role.'</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17.25" customHeight="1" s="26">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="3" t="n"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1" s="26">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" s="17" t="inlineStr">
-        <is>
-          <t>SPM-85-TC14</t>
-        </is>
-      </c>
+      <c r="B2" s="3" t="n"/>
     </row>
     <row r="3" ht="30.75" customHeight="1" s="26">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="B3" s="17" t="inlineStr">
-        <is>
-          <t>The Operations Manager has no Safety Checks link and is refused the Safety Checks page</t>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="inlineStr">
+        <is>
+          <t>SPM-85-TC14</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30.75" customHeight="1" s="26">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Pre-conditions</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="inlineStr">
-        <is>
-          <t>npm run fixtures:spm85 has been run. Logged in as Grace Lim (Operations Manager).</t>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="inlineStr">
+        <is>
+          <t>The Operations Manager has no Safety Checks link and is refused the Safety Checks page</t>
         </is>
       </c>
     </row>
     <row r="5" ht="57.75" customHeight="1" s="26">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>npm run fixtures:spm85 has been run. Logged in as Grace Lim (Operations Manager).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1" s="26">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>1. Look at the sidebar
 2. Type /safety-checks after the site address in the browser address bar (e.g. http://localhost:3000/safety-checks) and press Enter</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="44.25" customHeight="1" s="26">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7" ht="71.25" customHeight="1" s="26">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Operations Manager: grace.lim@connectsphere.com / password123
 Address: /safety-checks</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="71.25" customHeight="1" s="26">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="8" ht="17.25" customHeight="1" s="26">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>Step 1: The sidebar has no 'Safety Checks' link.
 Step 2: The Safety Checks page shows 'You do not have access to this' with 'The Operational Safety Check is the Safety Officer's role. You can still see the events you are involved in from your Dashboard.' No events are listed.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" s="26">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Created By</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>TAN JORDAN</t>
-        </is>
-      </c>
-    </row>
     <row r="9" ht="15.75" customHeight="1" s="26">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>TAN JORDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="26">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>Creation Date</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B10" s="9" t="n">
         <v>46307</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="26"/>
-    <row r="11" ht="15.75" customHeight="1" s="26">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="15.75" customHeight="1" s="26"/>
+    <row r="12" ht="57.75" customHeight="1" s="26">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="13" t="n"/>
-    </row>
-    <row r="12" ht="57.75" customHeight="1" s="26">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Actual Result</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Grace Lim's sidebar: Dashboard, Assignments, All Events, Venues, Notifications - no Safety Checks. /safety-checks showed 'You do not have access to this' with the same reason, and no rows.</t>
-        </is>
-      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
     </row>
     <row r="13" ht="17.25" customHeight="1" s="26">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Grace Lim's sidebar: Dashboard, Assignments, All Events, Venues, Notifications - no Safety Checks. /safety-checks showed 'You do not have access to this' with the same reason, and no rows.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="17.25" customHeight="1" s="26">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="15" ht="17.25" customHeight="1" s="26">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>TAN JORDAN</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="26">
       <c r="A16" s="14" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>TAN JORDAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" s="26">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B17" s="9" t="n">
         <v>46307</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" s="26"/>
-    <row r="18" ht="15.75" customHeight="1" s="26">
-      <c r="A18" s="10" t="inlineStr">
+    <row r="18" ht="15.75" customHeight="1" s="26"/>
+    <row r="19" ht="15.75" customHeight="1" s="26">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" s="26">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="B19" s="12" t="n"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="26">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>Step 1: The sidebar has no 'Safety Checks' link.
 Step 2: The Safety Checks page shows 'You do not have access to this' with 'The Operational Safety Check is the Safety Officer's role. You can still see the events you are involved in from your Dashboard.' No events are listed.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="26">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Pass/Fail/Not Executed/Blocked</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
     <row r="21" ht="15.75" customHeight="1" s="26">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Remarks</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="26">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Executed by</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>Kristen</t>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="26">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Kristen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="26">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
           <t>Date of Execution</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B24" s="9" t="n">
         <v>46307</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="26"/>
     <row r="25" ht="15.75" customHeight="1" s="26"/>
     <row r="26" ht="15.75" customHeight="1" s="26"/>
     <row r="27" ht="15.75" customHeight="1" s="26"/>
@@ -9791,6 +9807,9 @@
     <row r="999" ht="15.75" customHeight="1" s="26"/>
     <row r="1000" ht="15.75" customHeight="1" s="26"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -9824,7 +9843,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC01</t>
         </is>
@@ -9836,7 +9855,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer can log in and is shown as a Safety Officer</t>
         </is>
@@ -9848,7 +9867,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run (it creates the Safety Officer account Hana Yusof without reseeding). Logged out.</t>
         </is>
@@ -9860,7 +9879,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Open the Log in page
 2. Type hana.yusof@connectsphere.com in Email
@@ -9875,7 +9894,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Email: hana.yusof@connectsphere.com
 Password: password123
@@ -9889,7 +9908,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 4: The Dashboard opens. The account menu at the top shows 'Hana Yusof' with the role 'Safety Officer' underneath.</t>
         </is>
@@ -9901,7 +9920,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -9933,7 +9952,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Logging in as hana.yusof@connectsphere.com opened the Dashboard (/dashboard). The account menu at the top read 'Hana Yusof' with 'Safety Officer' underneath.</t>
         </is>
@@ -9957,7 +9976,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -9969,7 +9988,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -10000,7 +10019,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 4: The Dashboard opens. The account menu at the top shows 'Hana Yusof' with the role 'Safety Officer' underneath.</t>
         </is>
@@ -11063,7 +11082,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC02</t>
         </is>
@@ -11075,7 +11094,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>The public Create an account form does not offer the Safety Officer role</t>
         </is>
@@ -11087,7 +11106,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Logged out.</t>
         </is>
@@ -11099,7 +11118,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Open the Log in page
 2. Click 'Register'
@@ -11113,7 +11132,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Role dropdown on the Create an account page</t>
         </is>
@@ -11125,7 +11144,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 2: The Create an account page opens, and under 'Role' it says 'ConnectSphere staff accounts are created internally, not here.'
 Step 3: The dropdown offers only 'Event Organiser' and 'Attendee'. 'Safety Officer' is not an option, because it is an internal role.</t>
@@ -11138,7 +11157,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -11170,7 +11189,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Register opened the Create an account page, whose Role field says 'ConnectSphere staff accounts are created internally, not here.' The Role dropdown offered exactly 'Event Organiser' and 'Attendee'.</t>
         </is>
@@ -11194,7 +11213,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -11206,7 +11225,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -11237,7 +11256,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 2: The Create an account page opens, and under 'Role' it says 'ConnectSphere staff accounts are created internally, not here.'
 Step 3: The dropdown offers only 'Event Organiser' and 'Attendee'. 'Safety Officer' is not an option, because it is an internal role.</t>
@@ -11262,7 +11281,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -11274,7 +11293,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -12301,7 +12320,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC03</t>
         </is>
@@ -12313,7 +12332,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer's sidebar shows only Dashboard, Safety Checks, All Events and Notifications</t>
         </is>
@@ -12325,7 +12344,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -12337,7 +12356,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Look at the sidebar
 2. Click 'All Events' in the sidebar</t>
@@ -12350,7 +12369,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Safety Officer: hana.yusof@connectsphere.com
 Event: SPM85 Marina Networking Night (Planning)</t>
@@ -12363,7 +12382,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 1: The sidebar lists exactly 'Dashboard', 'Safety Checks', 'All Events' and 'Notifications'. 'Review Queue', 'Assignments', 'Venues', 'Booking Requests', 'Equipment', 'Equipment Requests', 'My Events', 'Browse Events' and 'My Registrations' are not shown.
 Step 2: The All Events list opens and includes 'SPM85 Marina Networking Night' with the status 'Planning'.</t>
@@ -12376,7 +12395,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -12408,7 +12427,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>The sidebar listed exactly Dashboard, Safety Checks, All Events, Notifications. All Events opened /events, whose list included 'SPM85 Marina Networking Night' (20 Sept 2027, 18:00-21:00, 50) with the status Planning.</t>
         </is>
@@ -12432,7 +12451,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -12444,7 +12463,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -12475,7 +12494,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 1: The sidebar lists exactly 'Dashboard', 'Safety Checks', 'All Events' and 'Notifications'. 'Review Queue', 'Assignments', 'Venues', 'Booking Requests', 'Equipment', 'Equipment Requests', 'My Events', 'Browse Events' and 'My Registrations' are not shown.
 Step 2: The All Events list opens and includes 'SPM85 Marina Networking Night' with the status 'Planning'.</t>
@@ -12500,7 +12519,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -12512,7 +12531,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -13539,7 +13558,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC04</t>
         </is>
@@ -13551,7 +13570,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>The Safety Checks list shows the events waiting for a safety check, and not events still being planned</t>
         </is>
@@ -13563,7 +13582,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. 'SPM85 Harbour Safety Forum' is in Safety review, submitted by Daniel Tan on 10 Oct 2026. 'SPM85 Marina Networking Night' is still in Planning. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -13575,7 +13594,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Click 'Safety Checks' in the sidebar</t>
         </is>
@@ -13587,7 +13606,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>In Safety review: SPM85 Harbour Safety Forum (Meridian Financial Group, 27 Sept 2027, 200 expected)
 In Planning: SPM85 Marina Networking Night</t>
@@ -13600,7 +13619,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 1: The Safety Checks page lists 'SPM85 Harbour Safety Forum' with Client 'Meridian Financial Group', When '27 Sept 2027, 09:00–17:00', Expected attendance '200' and Submitted '10 Oct 2026 by Daniel Tan'. 'SPM85 Marina Networking Night' is not listed, because it has not been submitted for a safety check.</t>
         </is>
@@ -13612,7 +13631,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -13644,7 +13663,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Safety Checks listed 'SPM85 Harbour Safety Forum' with Client 'Meridian Financial Group', When '27 Sept 2027, 09:00-17:00', Expected attendance '200' and Submitted '10 Oct 2026 by Daniel Tan'. 'SPM85 Marina Networking Night' was not listed.</t>
         </is>
@@ -13668,7 +13687,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>The list also holds other stories' events that are in Safety review (SPM-33, SPM-86 fixtures), which is correct: it shows every event waiting for a check.</t>
         </is>
@@ -13680,7 +13699,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -13711,7 +13730,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 1: The Safety Checks page lists 'SPM85 Harbour Safety Forum' with Client 'Meridian Financial Group', When '27 Sept 2027, 09:00–17:00', Expected attendance '200' and Submitted '10 Oct 2026 by Daniel Tan'. 'SPM85 Marina Networking Night' is not listed, because it has not been submitted for a safety check.</t>
         </is>
@@ -13735,7 +13754,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>The list also holds other stories' events that are in Safety review (SPM-33, SPM-86 fixtures), which is correct: it shows every event waiting for a check.</t>
         </is>
@@ -13747,7 +13766,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -14774,7 +14793,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC05</t>
         </is>
@@ -14786,7 +14805,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer sees the attendance, sessions, accessibility requirements and booked venues with capacity and layout on the event's Overview</t>
         </is>
@@ -14798,7 +14817,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -14810,7 +14829,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Click 'Safety Checks' in the sidebar
 2. Click 'SPM85 Harbour Safety Forum'</t>
@@ -14823,7 +14842,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Event: SPM85 Harbour Safety Forum
 Sessions: Main programme (27 Sept 2027 09:00-12:00, 200 people, Theatre) at Marina Auditorium (MAR-AUD), Theatre for 220; Breakout workshop (27 Sept 2027 13:00-17:00, 60 people, Classroom) at Orchard Seminar Room (ORC-SEM), Classroom for 70
@@ -14837,7 +14856,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 2: The event's Overview opens. Details shows Status 'Safety review' and Expected attendance '200'. A 'Sessions' card lists 'Main programme' as '27 Sept 2027, 09:00–12:00 · 200 people · Theatre' and 'Breakout workshop' as '27 Sept 2027, 13:00–17:00 · 60 people · Classroom'. A 'Venue bookings' card lists 'Main programme' as 'Marina Auditorium (MAR-AUD) · Theatre · seats 220' and 'Breakout workshop' as 'Orchard Seminar Room (ORC-SEM) · Classroom · seats 70'. 'Venue requirements' shows Required facilities 'Step-free access' and 'Hearing induction loop (nice-to-have)', and Accessibility notes 'Two wheelchair users attending; keep the aisle beside row A clear.'</t>
         </is>
@@ -14849,7 +14868,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -14881,7 +14900,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>The Overview showed Status 'Safety review' and Expected attendance '200'. Sessions: 'Main programme' '27 Sept 2027, 09:00-12:00 · 200 people · Theatre'; 'Breakout workshop' '27 Sept 2027, 13:00-17:00 · 60 people · Classroom'. Venue bookings: 'Main programme' 'Marina Auditorium (MAR-AUD) · Theatre · seats 220'; 'Breakout workshop' 'Orchard Seminar Room (ORC-SEM) · Classroom · seats 70'. Venue requirements: 'Step-free access', 'Hearing induction loop (nice-to-have)', and the accessibility note.</t>
         </is>
@@ -14905,7 +14924,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>The Classroom booking shows 70 seats - the capacity of the layout booked, not the room's largest (120).</t>
         </is>
@@ -14917,7 +14936,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -14948,7 +14967,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 2: The event's Overview opens. Details shows Status 'Safety review' and Expected attendance '200'. A 'Sessions' card lists 'Main programme' as '27 Sept 2027, 09:00–12:00 · 200 people · Theatre' and 'Breakout workshop' as '27 Sept 2027, 13:00–17:00 · 60 people · Classroom'. A 'Venue bookings' card lists 'Main programme' as 'Marina Auditorium (MAR-AUD) · Theatre · seats 220' and 'Breakout workshop' as 'Orchard Seminar Room (ORC-SEM) · Classroom · seats 70'. 'Venue requirements' shows Required facilities 'Step-free access' and 'Hearing induction loop (nice-to-have)', and Accessibility notes 'Two wheelchair users attending; keep the aisle beside row A clear.'</t>
         </is>
@@ -14972,7 +14991,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>The Classroom booking shows 70 seats - the capacity of the layout booked, not the room's largest (120).</t>
         </is>
@@ -14984,7 +15003,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -16011,7 +16030,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC06</t>
         </is>
@@ -16023,7 +16042,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer sees the event's equipment arrangements read-only</t>
         </is>
@@ -16035,7 +16054,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -16047,7 +16066,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Click 'Safety Checks' in the sidebar
 2. Click 'SPM85 Harbour Safety Forum'
@@ -16061,7 +16080,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Event: SPM85 Harbour Safety Forum
 Equipment: Handheld Wireless Mic x4 (Main programme, Reserved), Wheelchair Access Ramp x1 (Main programme, Reserved)</t>
@@ -16074,7 +16093,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 2: The tab bar shows only 'Overview' and 'Equipment'.
 Step 3: The Equipment requirements page lists 'Handheld Wireless Mic' (quantity 4) and 'Wheelchair Access Ramp' (quantity 1), each with the status 'Reserved'. There is no 'Add equipment' section and no 'Remove' button on either row.</t>
@@ -16087,7 +16106,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -16119,7 +16138,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>The tab bar showed only Overview and Equipment. The Equipment requirements page listed Handheld Wireless Mic (Main programme, Reserved, 4 reserved, Quantity 4) and Wheelchair Access Ramp (Main programme, Reserved, 1 reserved, Quantity 1). There was no 'Add equipment' section and no 'Remove' button.</t>
         </is>
@@ -16143,7 +16162,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -16155,7 +16174,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -16186,7 +16205,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 2: The tab bar shows only 'Overview' and 'Equipment'.
 Step 3: The Equipment requirements page lists 'Handheld Wireless Mic' (quantity 4) and 'Wheelchair Access Ramp' (quantity 1), each with the status 'Reserved'. There is no 'Add equipment' section and no 'Remove' button on either row.</t>
@@ -16211,7 +16230,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -16223,7 +16242,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -17250,7 +17269,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC07</t>
         </is>
@@ -17262,7 +17281,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer is offered no button that changes an event, its venue, its equipment or its registration</t>
         </is>
@@ -17274,7 +17293,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. 'SPM85 Riverside Product Launch' is Confirmed, open for registration, with an approved booking at Orchard Gallery. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -17286,7 +17305,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM85 Riverside Product Launch'</t>
@@ -17299,7 +17318,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Event: SPM85 Riverside Product Launch (Confirmed, registration open, Orchard Gallery (ORC-GAL), Theatre for 110)</t>
         </is>
@@ -17311,7 +17330,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 2: The Overview opens with Status 'Confirmed', and the 'Venue bookings' card lists 'Whole event' as 'Orchard Gallery (ORC-GAL) · Theatre · seats 110'. There is no 'Edit event information', 'Submit for safety check', 'Confirm event', 'Review request' or 'Record withdrawal' button, and the 'Registration' card has no 'Change registration settings' button. The tab bar shows only 'Overview' and 'Equipment', so there is no Venue tab to request or change a booking from.</t>
         </is>
@@ -17323,7 +17342,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -17355,7 +17374,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>The Overview showed Status 'Confirmed' and the Venue bookings card 'Whole event: Orchard Gallery (ORC-GAL) · Theatre · seats 110'. None of 'Edit event information', 'Submit for safety check', 'Confirm event', 'Review request', 'Record withdrawal' or 'Change registration settings' was offered. Tabs: Overview, Equipment.</t>
         </is>
@@ -17379,7 +17398,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -17391,7 +17410,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -17422,7 +17441,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 2: The Overview opens with Status 'Confirmed', and the 'Venue bookings' card lists 'Whole event' as 'Orchard Gallery (ORC-GAL) · Theatre · seats 110'. There is no 'Edit event information', 'Submit for safety check', 'Confirm event', 'Review request' or 'Record withdrawal' button, and the 'Registration' card has no 'Change registration settings' button. The tab bar shows only 'Overview' and 'Equipment', so there is no Venue tab to request or change a booking from.</t>
         </is>
@@ -17446,7 +17465,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -17458,7 +17477,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
@@ -18485,7 +18504,7 @@
           <t>Test Case ID</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>SPM-85-TC08</t>
         </is>
@@ -18497,7 +18516,7 @@
           <t>Summary</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>A Safety Officer who types the address of the Edit event information page is refused and shown no form</t>
         </is>
@@ -18509,7 +18528,7 @@
           <t>Pre-conditions</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>npm run fixtures:spm85 has been run. Logged in as Hana Yusof (Safety Officer).</t>
         </is>
@@ -18521,7 +18540,7 @@
           <t>Test Steps</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>1. Click 'All Events' in the sidebar
 2. Click 'SPM85 Riverside Product Launch' and note its reference (EVT-…) shown beside the title
@@ -18535,7 +18554,7 @@
           <t>Test Data</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>Event: SPM85 Riverside Product Launch
 Address: /events/&lt;reference&gt;/update</t>
@@ -18548,7 +18567,7 @@
           <t>Expected Result</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>Step 3: The page shows 'You can't edit this event's information' with 'Only the coordinator assigned to this event can change its information.' No information form and no 'Save' button are shown.</t>
         </is>
@@ -18560,7 +18579,7 @@
           <t>Created By</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -18592,7 +18611,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>Typing /events/&lt;reference&gt;/update showed 'You can't edit this event's information' with 'Only the coordinator assigned to this event can change its information.' No form field and no Save button.</t>
         </is>
@@ -18616,7 +18635,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -18628,7 +18647,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>TAN JORDAN</t>
         </is>
@@ -18659,7 +18678,7 @@
           <t>Actual Result</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>Step 3: The page shows 'You can't edit this event's information' with 'Only the coordinator assigned to this event can change its information.' No information form and no 'Save' button are shown.</t>
         </is>
@@ -18683,7 +18702,7 @@
           <t>Remarks</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -18695,7 +18714,7 @@
           <t>Executed by</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>Kristen</t>
         </is>
